--- a/company_data.xlsx
+++ b/company_data.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,44 @@
         </is>
       </c>
       <c r="L9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S-9009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1144,12 +1182,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-04-21 00:00:00</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-07-17 00:00:00</t>
+          <t>2027-01-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1157,7 +1195,11 @@
           <t>Alvarez</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Kaggwa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1590,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1636,15 +1678,10 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>date_done</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>date_completed</t>
         </is>
@@ -1693,15 +1730,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Monitor screen was replaced</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>2026-07-15 03:00:51.851000</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Monitor screen was replaced</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1746,15 +1782,14 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Valve bearings were replaced</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>2026-07-15 03:03:07.032000</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Valve bearings were replaced</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1797,15 +1832,58 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Client needs to add padding when keeping the item in storage.</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Client needs to add padding when keeping the item in storage.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-1004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M-001</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Infusion Pump A200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">testing </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kaggwa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/company_data.xlsx
+++ b/company_data.xlsx
@@ -470,7 +470,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,86 @@
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S-9010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kampala medical center</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S-9011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Infusion Pump A200</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1182,12 +1262,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2027-01-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1197,7 +1277,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kaggwa</t>
+          <t>Chen</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1494,12 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-15 00:00:00</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-13 00:00:00</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1427,7 +1507,11 @@
           <t>Kaggwa</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1513,7 +1597,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Resolved</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -1581,7 +1665,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>resolved</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -1632,7 +1716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1887,6 +1971,102 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R-1005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M-006</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ECG Machine E12</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kampala medical center</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>testing testing</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Alvarez</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R-1006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M-001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Infusion Pump A200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>testing testing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Chen</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Infusion Pump A200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company_data.xlsx
+++ b/company_data.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,178 @@
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S-9012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ultrasound U-Lite</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sunny medical center</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>S-9013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>St Micah hospital</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S-9014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ventilator V300</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trendi medical </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S-9015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Defibrillator DX</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1262,12 +1434,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2027-01-28</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1277,7 +1449,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Othieno</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1495,11 @@
           <t>Chen</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kumara</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1446,12 +1622,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-06 00:00:00</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-20 00:00:00</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1461,7 +1637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Kaggwa</t>
+          <t>Othieno</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1773,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -1665,7 +1841,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -1716,7 +1892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2067,6 +2243,102 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R-1007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M-005</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ultrasound U-Lite</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>St Micah hospital</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>creaking noise</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Othieno</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R-1008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M-001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Infusion Pump A200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sunny Imaging center</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>creaking noise</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Othieno</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Defibrillator DX</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>testing</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
